--- a/sources/sports_database.xlsx
+++ b/sources/sports_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,376 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025 TOPPS CHROME FOOTBALL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025-topps-chrome-football</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>wrestling</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026 UPPER DECK AEW WRESTLING</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-upper-deck-aew-wrestling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>soccer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2024 PANINI PRIZM SOCCER</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2024-panini-prizm-soccer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1996-97</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Skybox</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1996-97 SKYBOX PREMIUM BASKETBALL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1996-11-01</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1996-97-skybox-premium-basketball</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ufc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2024 TOPPS CHROME UFC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2024-topps-chrome-ufc</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2024 PANINI DONRUSS FOOTBALL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2024-panini-donruss-football</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>soccer</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025 TOPPS UEFA CLUB COMPETITIONS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-topps-uefa-club-competitions</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bandai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>carddass</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1989 BANDAI CARDDASS DRAGON BALL Z PART 1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1989-01-01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1989-bandai-carddass-dbz-part1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Meiji</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>promo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1998 MEIJI POKEMON GET CARD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1998-meiji-pokemon-get-card</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Impel</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>marvel</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1992 MARVEL UNIVERSE SERIES 1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1992-marvel-universe-series-1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
